--- a/results/Int Task Remove ACC -0.8/Linea_fi_all.xlsx
+++ b/results/Int Task Remove ACC -0.8/Linea_fi_all.xlsx
@@ -916,12 +916,12 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-0.010635696821515928 +/- 0.002298483579090835</t>
+          <t>-0.010605134474327671 +/- 0.002327759660675969</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>0.014486552567237087 +/- 0.0023243463743070265</t>
+          <t>0.014455990220048832 +/- 0.0023277596606759827</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -1681,7 +1681,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>-0.025626658802713122 +/- 0.0034250119220453766</t>
+          <t>-0.02565614862872314 +/- 0.0034817982054014458</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1891,7 +1891,7 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>0.029357798165137616 +/- 0.0036385659400541563</t>
+          <t>0.02938739271973957 +/- 0.0036028863415054095</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -2241,7 +2241,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>0.0013884785819793133 +/- 0.0007120809922123419</t>
+          <t>0.0013589364844903916 +/- 0.000701585943104157</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -2291,7 +2291,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>0.001683899556868529 +/- 0.002478897098469491</t>
+          <t>0.0016543574593796072 +/- 0.002454662106687253</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -2496,7 +2496,7 @@
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>-0.008301329394387057 +/- 0.0014973501799083334</t>
+          <t>-0.008360413589364901 +/- 0.001447562776957173</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
@@ -2671,7 +2671,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0.04212551805802254 +/- 0.0029987150449135446</t>
+          <t>0.042125518058022525 +/- 0.0030422358239353864</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -2686,7 +2686,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-0.004410894020130218 +/- 0.0012451001092251683</t>
+          <t>-0.004381290704558871 +/- 0.0012615320161434313</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -3351,12 +3351,12 @@
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>0.06906925728611722 +/- 0.005298277456698978</t>
+          <t>0.06903791914760264 +/- 0.005266392592344207</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>0.025195863365716088 +/- 0.003022790486189269</t>
+          <t>0.025227201504230655 +/- 0.003087244074015737</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
@@ -3561,7 +3561,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0.07822152886115447 +/- 0.0052005096116385695</t>
+          <t>0.07819032761310454 +/- 0.00517827929752879</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -3611,7 +3611,7 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>0.09419656786271453 +/- 0.004251735352930298</t>
+          <t>0.09422776911076444 +/- 0.004291731385722156</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -4041,7 +4041,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0.03309755378720898 +/- 0.0030516434395240514</t>
+          <t>0.033068081343943435 +/- 0.003082090530480724</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -4251,7 +4251,7 @@
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-0.00020630710285879372 +/- 0.002887848295964399</t>
+          <t>-0.00023577954612433727 +/- 0.0028780561428196345</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
@@ -4386,7 +4386,7 @@
       </c>
       <c r="CC9" t="inlineStr">
         <is>
-          <t>-0.02452107279693483 +/- 0.0029789045136441464</t>
+          <t>-0.024462127910403732 +/- 0.003002719864886528</t>
         </is>
       </c>
       <c r="CD9" t="inlineStr">
@@ -4451,7 +4451,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0.03560933448573903 +/- 0.0023694480201615774</t>
+          <t>0.03558052434456934 +/- 0.0023696231650795945</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -4781,7 +4781,7 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>0.005214635551714275 +/- 0.0007884720359207123</t>
+          <t>0.005214635551714275 +/- 0.0006872290660833595</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
@@ -4866,7 +4866,7 @@
       </c>
       <c r="CJ10" t="inlineStr">
         <is>
-          <t>0.042783059636992284 +/- 0.002770121666162239</t>
+          <t>0.04281186977816197 +/- 0.0027368117745982094</t>
         </is>
       </c>
       <c r="CK10" t="inlineStr">
@@ -4911,7 +4911,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-0.0011600237953599325 +/- 0.001306376636287792</t>
+          <t>-0.0012195121951219744 +/- 0.0013198517389847587</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -4921,7 +4921,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>0.11290898274836406 +/- 0.005504204170922269</t>
+          <t>0.11287923854848303 +/- 0.005450984752418008</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4941,7 +4941,7 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>0.14137418203450328 +/- 0.004028225703778093</t>
+          <t>0.1414039262343843 +/- 0.004017559549054867</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -4961,7 +4961,7 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>0.050029744199881 +/- 0.0031668843912447766</t>
+          <t>0.050089232599643055 +/- 0.0031652077559602672</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
@@ -5276,7 +5276,7 @@
       </c>
       <c r="CC11" t="inlineStr">
         <is>
-          <t>0.003093396787626379 +/- 0.0007063856089850196</t>
+          <t>0.003063652587745358 +/- 0.0007045044189367789</t>
         </is>
       </c>
       <c r="CD11" t="inlineStr">
